--- a/docs/PPG/Blog institucional.xlsx
+++ b/docs/PPG/Blog institucional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD474C9-2ADF-FE40-928F-866E3F22086C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C00C01E-0E58-3748-9D9F-EE997A6F0D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="680" windowWidth="27500" windowHeight="16900" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="248">
   <si>
     <t>Publicação</t>
   </si>
@@ -769,6 +769,15 @@
   </si>
   <si>
     <t>UNISUAM conquista prêmio no CONFIR 2025 com pesquisa inovadora em fisioterapia cardiovascular</t>
+  </si>
+  <si>
+    <t>https://www.unisuam.edu.br/noticias/stricto-sensu/unisuam-integra-pesquisa-internacional-sobre-exercicios-fisicos-no-controle-do-diabetes-tipo-2/</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>UNISUAM integra pesquisa internacional sobre exercícios físicos no controle do diabetes tipo 2</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF805655-101D-E249-A18A-A9A71B29B272}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -2704,6 +2713,20 @@
       </c>
       <c r="D111" s="2" t="s">
         <v>243</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B112" t="s">
+        <v>247</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -2814,6 +2837,7 @@
     <hyperlink ref="D109" r:id="rId104" xr:uid="{66E49DE5-F3CC-D846-8CCC-578F65D7F9D5}"/>
     <hyperlink ref="D110" r:id="rId105" xr:uid="{09E50F8E-B09E-8B4B-A158-896B00923BA9}"/>
     <hyperlink ref="D111" r:id="rId106" xr:uid="{A0CE41F5-AAB3-684F-9324-D30208A4B132}"/>
+    <hyperlink ref="D112" r:id="rId107" xr:uid="{96595E7A-B7BD-824C-8DC2-1A2BF78CC13D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/docs/PPG/Blog institucional.xlsx
+++ b/docs/PPG/Blog institucional.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C00C01E-0E58-3748-9D9F-EE997A6F0D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9A3C3A-DB14-C840-86A6-694AB1340848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="680" windowWidth="27500" windowHeight="16900" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
   <sheets>
     <sheet name="Blog" sheetId="17" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="250">
   <si>
     <t>Publicação</t>
   </si>
@@ -778,6 +778,12 @@
   </si>
   <si>
     <t>UNISUAM integra pesquisa internacional sobre exercícios físicos no controle do diabetes tipo 2</t>
+  </si>
+  <si>
+    <t>https://www.unisuam.edu.br/noticias/stricto-sensu/pesquisa-da-unisuam-publicada-em-revista-internacional-questiona-principio-tradicional-do-pilates/</t>
+  </si>
+  <si>
+    <t>Pesquisa da UNISUAM publicada em revista internacional questiona princípio tradicional do Pilates</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF805655-101D-E249-A18A-A9A71B29B272}">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -2727,6 +2733,20 @@
       </c>
       <c r="D112" s="2" t="s">
         <v>245</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B113" t="s">
+        <v>249</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -2838,6 +2858,7 @@
     <hyperlink ref="D110" r:id="rId105" xr:uid="{09E50F8E-B09E-8B4B-A158-896B00923BA9}"/>
     <hyperlink ref="D111" r:id="rId106" xr:uid="{A0CE41F5-AAB3-684F-9324-D30208A4B132}"/>
     <hyperlink ref="D112" r:id="rId107" xr:uid="{96595E7A-B7BD-824C-8DC2-1A2BF78CC13D}"/>
+    <hyperlink ref="D113" r:id="rId108" xr:uid="{F766E339-49B5-F248-8934-1FA00508F72B}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
